--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -92,7 +92,7 @@
 - code bunden till GrowthObservationTypeVS (IoÖ-specificerade SNOMED CT-koder)
 - value[x] begränsad till Quantity (pq-grenen; IoÖ anger alltid PQ-värden)
 - Enhet (UCUM) per mättyp: cm (längd/hC), kg (vikt), d (gestationslängd)
-Kodsystem för observationType.type: SNOMED CT SE, OID 1.2.752.116.2.1.1.
+Kodsystem för observationBody.type: SNOMED CT SE, OID 1.2.752.116.2.1.1.
 Täcker NPÖ 1.2 och 1177 Journal 1.2.</t>
   </si>
   <si>
@@ -908,7 +908,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Observationsstatus (observationBody.observationStatus – SNOMED CT urvals-id 56431000052106 → FHIR ObservationStatus via ConceptMap, se OBS-003)</t>
+    <t>Observationsstatus (observationBody.status – SNOMED CT urvals-id 56431000052106 → FHIR ObservationStatus via ConceptMap, se OBS-003)</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -972,7 +972,7 @@
 </t>
   </si>
   <si>
-    <t>IoÖ-kod (observationBody.observationType.type):
+    <t>IoÖ-kod (observationBody.type):
 SNOMED CT SE OID 1.2.752.116.2.1.1, kräver en av:
 1153637007 (kroppslängd), 50373000 (mått på kroppslängd),
 248334005 (längd i liggande – ej för nyanslutning),
@@ -1210,7 +1210,7 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t>observationBody.observationType.type.displayName</t>
+    <t>observationBody.type.displayName</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1238,7 +1238,7 @@
 </t>
   </si>
   <si>
-    <t>Patient (observationBody.patient.person.personId om tillgängligt; annars observationBody.patient.patientId)</t>
+    <t>Patient (observationBody.patient.person.id om tillgängligt; annars observationBody.patient.id)</t>
   </si>
   <si>
     <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
@@ -1327,7 +1327,7 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Observationstid (observationBody.time.ts → effectiveDateTime; observationBody.time.ivlts → effectivePeriod); se GENERAL-001 och OBS-001</t>
+    <t>Observationstid (observationBody.time.ts → effectiveDateTime; observationBody.time.ivl_ts → effectivePeriod); se GENERAL-001 och OBS-001</t>
   </si>
   <si>
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
@@ -1412,7 +1412,7 @@
 </t>
   </si>
   <si>
-    <t>Mätvärde (observationBody.observationValue.pq); IoÖ anger alltid pq-grenen för tillväxtmätningar</t>
+    <t>Mätvärde (observationBody.value.pq); IoÖ anger alltid pq-grenen för tillväxtmätningar</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1453,7 +1453,7 @@
 </t>
   </si>
   <si>
-    <t>Mätetalet (observationBody.observationValue.pq.value):
+    <t>Mätetalet (observationBody.value.pq.value):
 Längd: decimal cm, 0-1 decimal (t.ex. 49.5)
 Vikt:  decimal kg, 0-3 decimaler (t.ex. 5.830)
 Huvud: decimal cm, 1 decimal (t.ex. 38.5)

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSObservationGrowth.xlsx
+++ b/StructureDefinition-SEEHDSObservationGrowth.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3330" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3330" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -489,7 +489,7 @@
   <si>
     <t>Säkerhetsmärkning:
 confidentialityIndicator=true → v3-Confidentiality#R (skyddad identitet)
-approvedForPatient=false      → ActCode#NOPATIENT (ej visas för patient, se PDL-001)</t>
+approvedForPatient=false      → ActCode#NOPAT (ej visas för patient, se PDL-001)</t>
   </si>
   <si>
     <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
@@ -1850,6 +1850,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -10866,7 +10870,7 @@
         <v>580</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>581</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10875,10 +10879,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10889,10 +10893,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10918,10 +10922,10 @@
         <v>577</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10972,7 +10976,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10984,7 +10988,7 @@
         <v>580</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>581</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10993,10 +10997,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11007,10 +11011,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11036,16 +11040,16 @@
         <v>223</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11073,10 +11077,10 @@
         <v>173</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11094,7 +11098,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11112,10 +11116,10 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>513</v>
@@ -11129,10 +11133,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11158,16 +11162,16 @@
         <v>223</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11195,10 +11199,10 @@
         <v>159</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11216,7 +11220,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11234,10 +11238,10 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>513</v>
@@ -11251,10 +11255,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11277,17 +11281,17 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11336,7 +11340,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11360,7 +11364,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11371,10 +11375,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11400,10 +11404,10 @@
         <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11454,7 +11458,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11475,10 +11479,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11489,10 +11493,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11515,16 +11519,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11574,7 +11578,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11595,10 +11599,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11609,10 +11613,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11635,16 +11639,16 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11694,7 +11698,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11715,10 +11719,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11729,10 +11733,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11758,16 +11762,16 @@
         <v>561</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11816,7 +11820,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11837,10 +11841,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11851,10 +11855,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11969,10 +11973,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12089,10 +12093,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12211,10 +12215,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12240,13 +12244,13 @@
         <v>223</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>307</v>
@@ -12277,10 +12281,10 @@
         <v>159</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12298,7 +12302,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>93</v>
@@ -12316,7 +12320,7 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>311</v>
@@ -12333,10 +12337,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12359,16 +12363,16 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>443</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>445</v>
@@ -12420,7 +12424,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12438,7 +12442,7 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>448</v>
@@ -12455,10 +12459,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12484,13 +12488,13 @@
         <v>223</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>498</v>
@@ -12542,7 +12546,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12577,10 +12581,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12664,7 +12668,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12699,10 +12703,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12728,10 +12732,10 @@
         <v>83</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>564</v>
@@ -12786,7 +12790,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
